--- a/artfynd/A 38740-2026 artfynd.xlsx
+++ b/artfynd/A 38740-2026 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>136941105</v>
       </c>
       <c r="B4" t="n">
-        <v>111332</v>
+        <v>111338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>136941249</v>
       </c>
       <c r="B5" t="n">
-        <v>111332</v>
+        <v>111338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>136941079</v>
       </c>
       <c r="B6" t="n">
-        <v>106528</v>
+        <v>106534</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>136941163</v>
       </c>
       <c r="B7" t="n">
-        <v>106528</v>
+        <v>106534</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136941115</v>
       </c>
       <c r="B8" t="n">
-        <v>79076</v>
+        <v>79080</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>136941111</v>
       </c>
       <c r="B9" t="n">
-        <v>79153</v>
+        <v>79157</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38740-2026 artfynd.xlsx
+++ b/artfynd/A 38740-2026 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>136941105</v>
       </c>
       <c r="B4" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>136941249</v>
       </c>
       <c r="B5" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>136941079</v>
       </c>
       <c r="B6" t="n">
-        <v>106534</v>
+        <v>106536</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>136941163</v>
       </c>
       <c r="B7" t="n">
-        <v>106534</v>
+        <v>106536</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136941115</v>
       </c>
       <c r="B8" t="n">
-        <v>79080</v>
+        <v>79082</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>136941111</v>
       </c>
       <c r="B9" t="n">
-        <v>79157</v>
+        <v>79159</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38740-2026 artfynd.xlsx
+++ b/artfynd/A 38740-2026 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>136941105</v>
       </c>
       <c r="B4" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>136941249</v>
       </c>
       <c r="B5" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>136941079</v>
       </c>
       <c r="B6" t="n">
-        <v>106536</v>
+        <v>106537</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>136941163</v>
       </c>
       <c r="B7" t="n">
-        <v>106536</v>
+        <v>106537</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136941115</v>
       </c>
       <c r="B8" t="n">
-        <v>79082</v>
+        <v>79083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>136941111</v>
       </c>
       <c r="B9" t="n">
-        <v>79159</v>
+        <v>79160</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38740-2026 artfynd.xlsx
+++ b/artfynd/A 38740-2026 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>136941105</v>
       </c>
       <c r="B4" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>136941249</v>
       </c>
       <c r="B5" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>136941079</v>
       </c>
       <c r="B6" t="n">
-        <v>106537</v>
+        <v>106543</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>136941163</v>
       </c>
       <c r="B7" t="n">
-        <v>106537</v>
+        <v>106543</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38740-2026 artfynd.xlsx
+++ b/artfynd/A 38740-2026 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>136941105</v>
       </c>
       <c r="B4" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>136941249</v>
       </c>
       <c r="B5" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>136941079</v>
       </c>
       <c r="B6" t="n">
-        <v>106543</v>
+        <v>106547</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>136941163</v>
       </c>
       <c r="B7" t="n">
-        <v>106543</v>
+        <v>106547</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136941115</v>
       </c>
       <c r="B8" t="n">
-        <v>79083</v>
+        <v>79085</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>136941111</v>
       </c>
       <c r="B9" t="n">
-        <v>79160</v>
+        <v>79162</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38740-2026 artfynd.xlsx
+++ b/artfynd/A 38740-2026 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>136941105</v>
       </c>
       <c r="B4" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>136941249</v>
       </c>
       <c r="B5" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>136941079</v>
       </c>
       <c r="B6" t="n">
-        <v>106547</v>
+        <v>106549</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>136941163</v>
       </c>
       <c r="B7" t="n">
-        <v>106547</v>
+        <v>106549</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38740-2026 artfynd.xlsx
+++ b/artfynd/A 38740-2026 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>136941105</v>
       </c>
       <c r="B4" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>136941249</v>
       </c>
       <c r="B5" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>136941079</v>
       </c>
       <c r="B6" t="n">
-        <v>106549</v>
+        <v>106551</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>136941163</v>
       </c>
       <c r="B7" t="n">
-        <v>106549</v>
+        <v>106551</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136941115</v>
       </c>
       <c r="B8" t="n">
-        <v>79085</v>
+        <v>79088</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>136941111</v>
       </c>
       <c r="B9" t="n">
-        <v>79162</v>
+        <v>79165</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38740-2026 artfynd.xlsx
+++ b/artfynd/A 38740-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136941126</v>
       </c>
       <c r="B2" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>136941213</v>
       </c>
       <c r="B3" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>136941105</v>
       </c>
       <c r="B4" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>136941249</v>
       </c>
       <c r="B5" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>136941079</v>
       </c>
       <c r="B6" t="n">
-        <v>106551</v>
+        <v>106564</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>136941163</v>
       </c>
       <c r="B7" t="n">
-        <v>106551</v>
+        <v>106564</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136941115</v>
       </c>
       <c r="B8" t="n">
-        <v>79088</v>
+        <v>79101</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>136941111</v>
       </c>
       <c r="B9" t="n">
-        <v>79165</v>
+        <v>79178</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38740-2026 artfynd.xlsx
+++ b/artfynd/A 38740-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136941126</v>
       </c>
       <c r="B2" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>136941213</v>
       </c>
       <c r="B3" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>136941105</v>
       </c>
       <c r="B4" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>136941249</v>
       </c>
       <c r="B5" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>136941079</v>
       </c>
       <c r="B6" t="n">
-        <v>106564</v>
+        <v>106566</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>136941163</v>
       </c>
       <c r="B7" t="n">
-        <v>106564</v>
+        <v>106566</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136941115</v>
       </c>
       <c r="B8" t="n">
-        <v>79101</v>
+        <v>79103</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>136941111</v>
       </c>
       <c r="B9" t="n">
-        <v>79178</v>
+        <v>79180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38740-2026 artfynd.xlsx
+++ b/artfynd/A 38740-2026 artfynd.xlsx
@@ -715,11 +715,7 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -838,11 +834,7 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -1072,11 +1064,7 @@
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">

--- a/artfynd/A 38740-2026 artfynd.xlsx
+++ b/artfynd/A 38740-2026 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>136941105</v>
       </c>
       <c r="B4" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>136941249</v>
       </c>
       <c r="B5" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>136941079</v>
       </c>
       <c r="B6" t="n">
-        <v>106566</v>
+        <v>106570</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>136941163</v>
       </c>
       <c r="B7" t="n">
-        <v>106566</v>
+        <v>106570</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38740-2026 artfynd.xlsx
+++ b/artfynd/A 38740-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136941126</v>
       </c>
       <c r="B2" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>136941213</v>
       </c>
       <c r="B3" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>136941105</v>
       </c>
       <c r="B4" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>136941249</v>
       </c>
       <c r="B5" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>136941079</v>
       </c>
       <c r="B6" t="n">
-        <v>106570</v>
+        <v>106590</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>136941163</v>
       </c>
       <c r="B7" t="n">
-        <v>106570</v>
+        <v>106590</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>136941115</v>
       </c>
       <c r="B8" t="n">
-        <v>79103</v>
+        <v>79113</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>136941111</v>
       </c>
       <c r="B9" t="n">
-        <v>79180</v>
+        <v>79190</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38740-2026 artfynd.xlsx
+++ b/artfynd/A 38740-2026 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>136941105</v>
       </c>
       <c r="B4" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>136941249</v>
       </c>
       <c r="B5" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>136941079</v>
       </c>
       <c r="B6" t="n">
-        <v>106590</v>
+        <v>106591</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>136941163</v>
       </c>
       <c r="B7" t="n">
-        <v>106590</v>
+        <v>106591</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38740-2026 artfynd.xlsx
+++ b/artfynd/A 38740-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136941126</v>
       </c>
       <c r="B2" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>136941213</v>
       </c>
       <c r="B3" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>136941105</v>
       </c>
       <c r="B4" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>136941249</v>
       </c>
       <c r="B5" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>136941079</v>
       </c>
       <c r="B6" t="n">
-        <v>106591</v>
+        <v>106596</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>136941163</v>
       </c>
       <c r="B7" t="n">
-        <v>106591</v>
+        <v>106596</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>136941115</v>
       </c>
       <c r="B8" t="n">
-        <v>79113</v>
+        <v>79116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>136941111</v>
       </c>
       <c r="B9" t="n">
-        <v>79190</v>
+        <v>79193</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38740-2026 artfynd.xlsx
+++ b/artfynd/A 38740-2026 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>136941105</v>
       </c>
       <c r="B4" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>136941249</v>
       </c>
       <c r="B5" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>136941079</v>
       </c>
       <c r="B6" t="n">
-        <v>106596</v>
+        <v>106599</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>136941163</v>
       </c>
       <c r="B7" t="n">
-        <v>106596</v>
+        <v>106599</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38740-2026 artfynd.xlsx
+++ b/artfynd/A 38740-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136941126</v>
       </c>
       <c r="B2" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>136941213</v>
       </c>
       <c r="B3" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>136941105</v>
       </c>
       <c r="B4" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>136941249</v>
       </c>
       <c r="B5" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>136941079</v>
       </c>
       <c r="B6" t="n">
-        <v>106599</v>
+        <v>106605</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>136941163</v>
       </c>
       <c r="B7" t="n">
-        <v>106599</v>
+        <v>106605</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>136941115</v>
       </c>
       <c r="B8" t="n">
-        <v>79116</v>
+        <v>79121</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>136941111</v>
       </c>
       <c r="B9" t="n">
-        <v>79193</v>
+        <v>79198</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38740-2026 artfynd.xlsx
+++ b/artfynd/A 38740-2026 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>136941105</v>
       </c>
       <c r="B4" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>136941249</v>
       </c>
       <c r="B5" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>136941079</v>
       </c>
       <c r="B6" t="n">
-        <v>106605</v>
+        <v>106606</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>136941163</v>
       </c>
       <c r="B7" t="n">
-        <v>106605</v>
+        <v>106606</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38740-2026 artfynd.xlsx
+++ b/artfynd/A 38740-2026 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>136941105</v>
       </c>
       <c r="B4" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>136941249</v>
       </c>
       <c r="B5" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>136941079</v>
       </c>
       <c r="B6" t="n">
-        <v>106606</v>
+        <v>106618</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>136941163</v>
       </c>
       <c r="B7" t="n">
-        <v>106606</v>
+        <v>106618</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>136941115</v>
       </c>
       <c r="B8" t="n">
-        <v>79121</v>
+        <v>79132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>136941111</v>
       </c>
       <c r="B9" t="n">
-        <v>79198</v>
+        <v>79209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38740-2026 artfynd.xlsx
+++ b/artfynd/A 38740-2026 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>136941105</v>
       </c>
       <c r="B4" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>136941249</v>
       </c>
       <c r="B5" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>136941079</v>
       </c>
       <c r="B6" t="n">
-        <v>106618</v>
+        <v>106619</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>136941163</v>
       </c>
       <c r="B7" t="n">
-        <v>106618</v>
+        <v>106619</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>136941115</v>
       </c>
       <c r="B8" t="n">
-        <v>79132</v>
+        <v>79133</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>136941111</v>
       </c>
       <c r="B9" t="n">
-        <v>79209</v>
+        <v>79210</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38740-2026 artfynd.xlsx
+++ b/artfynd/A 38740-2026 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>136941105</v>
       </c>
       <c r="B4" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>136941249</v>
       </c>
       <c r="B5" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>136941079</v>
       </c>
       <c r="B6" t="n">
-        <v>106619</v>
+        <v>106622</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>136941163</v>
       </c>
       <c r="B7" t="n">
-        <v>106619</v>
+        <v>106622</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>136941115</v>
       </c>
       <c r="B8" t="n">
-        <v>79133</v>
+        <v>79135</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>136941111</v>
       </c>
       <c r="B9" t="n">
-        <v>79210</v>
+        <v>79212</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38740-2026 artfynd.xlsx
+++ b/artfynd/A 38740-2026 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>136941105</v>
       </c>
       <c r="B4" t="n">
-        <v>111430</v>
+        <v>111432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>136941249</v>
       </c>
       <c r="B5" t="n">
-        <v>111430</v>
+        <v>111432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>136941079</v>
       </c>
       <c r="B6" t="n">
-        <v>106622</v>
+        <v>106624</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>136941163</v>
       </c>
       <c r="B7" t="n">
-        <v>106622</v>
+        <v>106624</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>136941115</v>
       </c>
       <c r="B8" t="n">
-        <v>79135</v>
+        <v>79136</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>136941111</v>
       </c>
       <c r="B9" t="n">
-        <v>79212</v>
+        <v>79213</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38740-2026 artfynd.xlsx
+++ b/artfynd/A 38740-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136941126</v>
       </c>
       <c r="B2" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>136941213</v>
       </c>
       <c r="B3" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>136941105</v>
       </c>
       <c r="B4" t="n">
-        <v>111432</v>
+        <v>111436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>136941249</v>
       </c>
       <c r="B5" t="n">
-        <v>111432</v>
+        <v>111436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>136941079</v>
       </c>
       <c r="B6" t="n">
-        <v>106624</v>
+        <v>106628</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>136941163</v>
       </c>
       <c r="B7" t="n">
-        <v>106624</v>
+        <v>106628</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>136941115</v>
       </c>
       <c r="B8" t="n">
-        <v>79136</v>
+        <v>79139</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>136941111</v>
       </c>
       <c r="B9" t="n">
-        <v>79213</v>
+        <v>79216</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
